--- a/data/dividends_info_20260328.xlsx
+++ b/data/dividends_info_20260328.xlsx
@@ -6515,7 +6515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C274"/>
+  <dimension ref="A1:C234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6555,7 +6555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6572,7 +6572,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6589,7 +6589,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6606,7 +6606,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6623,7 +6623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6640,7 +6640,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6657,7 +6657,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6674,7 +6674,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6684,14 +6684,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6708,7 +6708,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6725,7 +6725,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6742,7 +6742,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6759,7 +6759,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6769,14 +6769,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6786,14 +6786,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6810,7 +6810,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6827,7 +6827,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6844,7 +6844,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6861,7 +6861,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6871,14 +6871,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6895,7 +6895,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6929,7 +6929,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6946,7 +6946,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6963,7 +6963,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6997,7 +6997,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7014,7 +7014,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7048,7 +7048,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7065,7 +7065,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7082,7 +7082,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7099,7 +7099,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7116,7 +7116,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7133,7 +7133,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7160,19 +7160,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7184,46 +7184,46 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7235,12 +7235,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7252,12 +7252,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7269,12 +7269,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7286,12 +7286,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7303,12 +7303,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7320,24 +7320,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7347,14 +7347,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7388,7 +7388,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7398,14 +7398,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7422,7 +7422,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7432,14 +7432,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7456,7 +7456,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7473,7 +7473,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7490,7 +7490,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7500,14 +7500,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7524,7 +7524,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7541,7 +7541,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7558,7 +7558,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7575,7 +7575,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7602,14 +7602,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7626,7 +7626,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7643,7 +7643,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7660,7 +7660,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7670,14 +7670,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7694,7 +7694,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7711,7 +7711,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7755,70 +7755,70 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7830,80 +7830,80 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7915,12 +7915,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7932,12 +7932,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7949,46 +7949,46 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8000,63 +8000,63 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8068,12 +8068,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8085,165 +8085,165 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8255,29 +8255,29 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8289,46 +8289,46 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8340,29 +8340,29 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8374,24 +8374,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8425,7 +8425,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8435,14 +8435,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8452,14 +8452,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8476,7 +8476,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8493,7 +8493,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8503,14 +8503,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8527,7 +8527,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8544,7 +8544,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8561,7 +8561,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8578,97 +8578,97 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8680,12 +8680,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8697,80 +8697,80 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8782,46 +8782,46 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8833,12 +8833,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8850,12 +8850,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8867,46 +8867,46 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8918,46 +8918,46 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8969,63 +8969,63 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9037,29 +9037,29 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9071,29 +9071,29 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9105,29 +9105,29 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9139,63 +9139,63 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9207,29 +9207,29 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9241,12 +9241,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9258,114 +9258,114 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9377,12 +9377,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9394,12 +9394,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9411,12 +9411,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9428,12 +9428,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9445,29 +9445,29 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9479,24 +9479,24 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9506,19 +9506,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9530,12 +9530,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9547,29 +9547,29 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -9581,12 +9581,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9598,29 +9598,29 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -9632,12 +9632,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -9649,12 +9649,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -9666,12 +9666,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -9683,12 +9683,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -9700,12 +9700,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -9717,12 +9717,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9734,12 +9734,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9751,12 +9751,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9768,12 +9768,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -9785,12 +9785,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9802,46 +9802,46 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -9853,7 +9853,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -9870,7 +9870,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9887,7 +9887,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9904,7 +9904,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9921,7 +9921,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9955,7 +9955,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9972,46 +9972,46 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -10023,12 +10023,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -10040,29 +10040,29 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -10074,29 +10074,29 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -10108,12 +10108,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -10125,12 +10125,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -10142,12 +10142,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -10159,12 +10159,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -10176,12 +10176,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -10193,12 +10193,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -10210,12 +10210,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -10227,12 +10227,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10244,12 +10244,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10261,12 +10261,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -10278,12 +10278,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10295,12 +10295,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -10312,12 +10312,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -10329,12 +10329,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -10346,12 +10346,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -10363,46 +10363,46 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10414,63 +10414,63 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -10482,695 +10482,15 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Matica Fintec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>AEDES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>PININFARINA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Pharmanutra S.p.A.</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>SIAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>SOGEFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>RES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>SECO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>FNM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>FRENDY ENERGY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Allcore S.p.A.</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Alfonsino S.p.A.</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Acinque S.p.A.</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Gambero Rosso S.p.A.</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Grifal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>rino petino S.p.A.</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -11200,554 +10520,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Acinque S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Alfonsino S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Allcore S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>FNM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FRENDY ENERGY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gambero Rosso S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Grifal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PININFARINA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pharmanutra S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Poste Italiane S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SECO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SIAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>SOGEFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>rino petino S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>